--- a/input/images/tables/profile_metadata.xlsx
+++ b/input/images/tables/profile_metadata.xlsx
@@ -418,7 +418,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>﻿Is_New</t>
+          <t>Is_New</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>in version 9.0.0 removed the term "implantable" form the official ( canonical ) URL,  name,  and title.</t>
+          <t>in version 9.0.0 removed the term "implantable" from the official ( canonical ) URL,  name,  and title.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -6036,7 +6036,11 @@
       <c r="AF63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B64" t="n">
         <v>76</v>
       </c>

--- a/input/images/tables/profile_metadata.xlsx
+++ b/input/images/tables/profile_metadata.xlsx
@@ -508,72 +508,107 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>conf_req</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>data_element</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>resource_type</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cat1_scope</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>cat1_scope_conf</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>cat1_scope_conf_req</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>cat2_scope</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>cat2_scope_conf</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>cat2_scope_conf_req</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
         <is>
           <t>cat3_scope</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>cat3_scope_conf</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>cat3_scope_conf_req</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>cat4_scope</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>cat4_scope_conf</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>cat4_scope_conf_req</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
         <is>
           <t>cat5_scope</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>cat5_scope_conf</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>cat5_scope_conf_req</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
         <is>
           <t>cat6_scope</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>cat6_scope_conf</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>cat6_scope_conf_req</t>
         </is>
       </c>
     </row>
@@ -640,15 +675,19 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
+          <t>CONF-0132</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>allergy and intolerance</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>AllergyIntolerance</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
@@ -660,6 +699,13 @@
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -728,15 +774,19 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
+          <t>CONF-0133</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>care plan</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>CarePlan</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
@@ -748,6 +798,13 @@
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -812,15 +869,19 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
+          <t>CONF-0134</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>careteam</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>CareTeam</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -832,6 +893,13 @@
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -900,26 +968,34 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>CONF-0135</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>encounter diagnosis</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/condition-category|encounter-diagnosis</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>CONF-0159</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -928,6 +1004,13 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -996,42 +1079,61 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>CONF-0135</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>problems and health concern</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/condition-category|problem-list-item</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>CONF-0160</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>http://hl7.org/fhir/us/core/CodeSystem/condition-category|health-concern</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>CONF-0158</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -1096,15 +1198,19 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>CONF-0136</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>coverage</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -1116,6 +1222,13 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1184,15 +1297,19 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
+          <t>CONF-0137</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>medical device</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Device</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
@@ -1204,6 +1321,13 @@
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -1268,38 +1392,49 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
+          <t>CONF-0138</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>clinical note</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>DiagnosticReport</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>http://loinc.org|LP29684-5</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">http://loinc.org|LP29708-2	</t>
-        </is>
-      </c>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t xml:space="preserve">http://loinc.org|LP7839-6		</t>
+          <t xml:space="preserve">http://loinc.org|LP29708-2	</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http://loinc.org|LP7839-6		</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -1364,20 +1499,24 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
+          <t>CONF-0138</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>laboratory</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>DiagnosticReport</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/v2-0074|LAB</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
@@ -1388,6 +1527,13 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1452,26 +1598,34 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>clniical note</t>
+          <t>CONF-0139</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>clinical note</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>DocumentReference</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-documentreference-category|clinical-note</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SHOULD</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>CONF-0166</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
@@ -1480,6 +1634,13 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1544,15 +1705,19 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
+          <t>CONF-0140</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>encounter</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Encounter</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
@@ -1564,6 +1729,13 @@
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1628,15 +1800,19 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
+          <t>CONF-0141</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>goal</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Goal</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
@@ -1648,6 +1824,13 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -1712,15 +1895,19 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
+          <t>CONF-0142</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>immunization</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Immunization</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -1732,6 +1919,13 @@
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -1794,13 +1988,17 @@
           <t>MAY</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr">
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>CONF-0156</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -1812,6 +2010,13 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1874,13 +2079,17 @@
           <t>MAY</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr">
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>CONF-0157</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
         <is>
           <t>Medication</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -1892,6 +2101,13 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -1956,15 +2172,19 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
+          <t>CONF-0143</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>prescription</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -1976,6 +2196,13 @@
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -2040,15 +2267,19 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
+          <t>CONF-0144</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>dispensed medication</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>MedicationDispense</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
@@ -2060,6 +2291,13 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -2128,26 +2366,34 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>laboratory</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|laboratory</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>CONF-0163</t>
+        </is>
+      </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
@@ -2156,6 +2402,13 @@
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -2220,26 +2473,34 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>social history</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org//CodeSystem-observation-category|social-history</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>CONF-0162</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
@@ -2248,6 +2509,13 @@
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -2312,26 +2580,34 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
           <t>social history</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org//CodeSystem-observation-category|social-history</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>CONF-0162</t>
+        </is>
+      </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
@@ -2340,6 +2616,13 @@
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -2404,26 +2687,34 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
           <t>social history</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org//CodeSystem-observation-category|social-history</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>CONF-0162</t>
+        </is>
+      </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
@@ -2432,6 +2723,13 @@
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -2500,26 +2798,34 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
           <t>vital signs</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
@@ -2528,6 +2834,13 @@
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -2596,50 +2909,65 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
           <t>assessment</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|sdoh</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>CONF-0161</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
         <is>
           <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|functional-status</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr">
         <is>
           <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|disability-status</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr">
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
         <is>
           <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|cognitive-status</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr">
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|activity</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -2708,26 +3036,34 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
           <t>vital signs</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
@@ -2736,6 +3072,13 @@
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -2804,26 +3147,34 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
           <t>vital signs</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
@@ -2832,6 +3183,13 @@
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -2900,26 +3258,34 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
           <t>vital signs</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
@@ -2928,6 +3294,13 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -2996,26 +3369,34 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
           <t>vital signs</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
@@ -3024,6 +3405,13 @@
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -3088,26 +3476,34 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
           <t>social history</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org//CodeSystem-observation-category|social-history</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>CONF-0162</t>
+        </is>
+      </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
@@ -3116,6 +3512,13 @@
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -3184,26 +3587,34 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
           <t>social history</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org//CodeSystem-observation-category|social-history</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>CONF-0162</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
@@ -3212,6 +3623,13 @@
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -3280,26 +3698,34 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
           <t>vital signs</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
@@ -3308,6 +3734,13 @@
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -3376,26 +3809,34 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
           <t>vital signs</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
@@ -3404,6 +3845,13 @@
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -3472,26 +3920,34 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
           <t>vital signs</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
@@ -3500,6 +3956,13 @@
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -3568,58 +4031,77 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
           <t>assessment</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|survey</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>CONF-0164</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
         <is>
           <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|sdoh</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>CONF-0161</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
         <is>
           <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|functional-status</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|disability-status</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|cognitive-status</t>
-        </is>
-      </c>
+      <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr">
         <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|disability-status</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|cognitive-status</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr">
+        <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|activity</t>
         </is>
       </c>
-      <c r="AF34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -3684,26 +4166,34 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
           <t>vital signs</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
@@ -3712,6 +4202,13 @@
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -3780,26 +4277,34 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
           <t>vital signs</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
@@ -3808,6 +4313,13 @@
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -3876,38 +4388,49 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
           <t>clinical results</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|laboratory</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>http://terminology.hl7.org/CodeSystem/observation-category|imaging</t>
-        </is>
-      </c>
+      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/CodeSystem/observation-category|procedure</t>
+          <t>http://terminology.hl7.org/CodeSystem/observation-category|imaging</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>http://terminology.hl7.org/CodeSystem/observation-category|procedure</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -3976,26 +4499,34 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
           <t>vital signs</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
@@ -4004,6 +4535,13 @@
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -4072,26 +4610,34 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
           <t>vital signs</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
@@ -4100,6 +4646,13 @@
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -4168,26 +4721,34 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
           <t>vital signs</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
@@ -4196,6 +4757,13 @@
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -4264,26 +4832,34 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
           <t>vital signs</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr"/>
@@ -4292,6 +4868,13 @@
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -4356,15 +4939,19 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
+          <t>CONF-0146</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
           <t>organization</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>Organization</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
@@ -4376,6 +4963,13 @@
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -4440,15 +5034,19 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
+          <t>CONF-0147</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
           <t>patient</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>Patient</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
@@ -4460,6 +5058,13 @@
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -4524,15 +5129,19 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
+          <t>CONF-0148</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
           <t>practitioner</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>Practitioner</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
@@ -4544,6 +5153,13 @@
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -4608,15 +5224,19 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
+          <t>CONF-0149</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
           <t>practitioner role</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>PractitionerRole</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
@@ -4628,6 +5248,13 @@
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -4692,15 +5319,19 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
+          <t>CONF-0150</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
           <t>procedure</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>Procedure</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
@@ -4712,6 +5343,13 @@
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -4776,15 +5414,19 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
+          <t>CONF-0151</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
           <t>provenance</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>Provenance</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
@@ -4796,6 +5438,13 @@
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -4860,15 +5509,19 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
+          <t>CONF-0152</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
           <t>completed questionnnaire, survey and assessement</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>QuestionnaireResponse</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
@@ -4880,6 +5533,13 @@
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -4944,15 +5604,19 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
+          <t>CONF-0153</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
           <t>related person</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>RelatedPerson</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
@@ -4964,6 +5628,13 @@
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -5028,42 +5699,53 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
+          <t>CONF-0154</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
           <t>order and referral</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>ServiceRequest</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|sdoh</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>MAY</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|functional-status</t>
         </is>
       </c>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>http://snomed.info/sct|surgical-procedure</t>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|functional-status</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>http://snomed.info/sct|surgical-procedure</t>
+        </is>
+      </c>
       <c r="AC50" t="inlineStr"/>
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
@@ -5128,15 +5810,19 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
+          <t>CONF-0155</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
           <t>specimen</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>Specimen</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
@@ -5148,6 +5834,13 @@
       <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -5212,25 +5905,29 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
           <t>treatment intervention preference</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|treatment-intervention-preference</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
@@ -5240,6 +5937,13 @@
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
@@ -5304,25 +6008,29 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
           <t>care experience preference</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|care-experience-preference</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
@@ -5332,6 +6040,13 @@
       <c r="AD53" t="inlineStr"/>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
@@ -5396,15 +6111,19 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
+          <t>CONF-0909</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
           <t>family health history</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>FamilyMemberHistory</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
@@ -5416,6 +6135,13 @@
       <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
@@ -5455,12 +6181,12 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr">
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
         <is>
           <t>MedicationStatement</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
@@ -5472,6 +6198,13 @@
       <c r="AD55" t="inlineStr"/>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
@@ -5519,12 +6252,12 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr">
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
@@ -5536,6 +6269,13 @@
       <c r="AD56" t="inlineStr"/>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
@@ -5598,17 +6338,17 @@
           <t>SHALL</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr">
         <is>
           <t>adi</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>DocumentReference</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
@@ -5620,6 +6360,13 @@
       <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -5682,17 +6429,17 @@
           <t>SHALL</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr">
         <is>
           <t>adi</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
@@ -5704,6 +6451,13 @@
       <c r="AD58" t="inlineStr"/>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
@@ -5753,12 +6507,12 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr">
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
@@ -5770,6 +6524,13 @@
       <c r="AD59" t="inlineStr"/>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -5819,12 +6580,12 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr">
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
@@ -5836,6 +6597,13 @@
       <c r="AD60" t="inlineStr"/>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -5885,12 +6653,12 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr">
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
@@ -5902,6 +6670,13 @@
       <c r="AD61" t="inlineStr"/>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
@@ -5951,12 +6726,12 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr">
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
@@ -5968,6 +6743,13 @@
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -6017,12 +6799,12 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr">
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
@@ -6034,6 +6816,13 @@
       <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6089,12 +6878,12 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr">
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
         <is>
           <t>Extension</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
@@ -6106,6 +6895,13 @@
       <c r="AD64" t="inlineStr"/>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
@@ -6165,12 +6961,12 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr">
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
         <is>
           <t>Extension</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
@@ -6182,6 +6978,13 @@
       <c r="AD65" t="inlineStr"/>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
@@ -6237,12 +7040,12 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr">
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
         <is>
           <t>Extension</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
@@ -6254,6 +7057,13 @@
       <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
@@ -6311,12 +7121,12 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr">
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
         <is>
           <t>Extension</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
@@ -6328,6 +7138,13 @@
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
@@ -6379,12 +7196,12 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr">
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
         <is>
           <t>Extension</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
@@ -6396,6 +7213,13 @@
       <c r="AD68" t="inlineStr"/>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
@@ -6447,12 +7271,12 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr">
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
         <is>
           <t>Extension</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
@@ -6464,6 +7288,13 @@
       <c r="AD69" t="inlineStr"/>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
@@ -6523,12 +7354,12 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr">
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr">
         <is>
           <t>Extension</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
@@ -6540,6 +7371,13 @@
       <c r="AD70" t="inlineStr"/>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
@@ -6591,12 +7429,12 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr">
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr">
         <is>
           <t>Extension</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
@@ -6608,6 +7446,13 @@
       <c r="AD71" t="inlineStr"/>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
@@ -6667,12 +7512,12 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr">
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr">
         <is>
           <t>Extension</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
@@ -6684,6 +7529,13 @@
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
@@ -6739,12 +7591,12 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr">
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr">
         <is>
           <t>Extension</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
@@ -6756,6 +7608,13 @@
       <c r="AD73" t="inlineStr"/>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -6807,12 +7666,12 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr">
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr">
         <is>
           <t>Extension</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
@@ -6824,6 +7683,13 @@
       <c r="AD74" t="inlineStr"/>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
@@ -6883,12 +7749,12 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr">
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr">
         <is>
           <t>Extension</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
@@ -6900,6 +7766,13 @@
       <c r="AD75" t="inlineStr"/>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr"/>
+      <c r="AM75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
@@ -6953,12 +7826,12 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr">
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr">
         <is>
           <t>Extension</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr"/>
@@ -6970,6 +7843,13 @@
       <c r="AD76" t="inlineStr"/>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -7021,12 +7901,12 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr">
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr">
         <is>
           <t>Extension</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -7038,6 +7918,13 @@
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
@@ -7110,6 +7997,13 @@
       <c r="AD78" t="inlineStr"/>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/input/images/tables/profile_metadata.xlsx
+++ b/input/images/tables/profile_metadata.xlsx
@@ -6825,11 +6825,7 @@
       <c r="AM63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
         <v>76</v>
       </c>
